--- a/data/pack/us/us_energy_input_index.xlsx
+++ b/data/pack/us/us_energy_input_index.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K69"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4229,6 +4229,61 @@
         </is>
       </c>
       <c r="K69" t="inlineStr">
+        <is>
+          <t>Source: USDA National Agricultural Statistics Service (NASS), Quick Stats</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>us_energy_input_index</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>us_energy_input_index</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>index_2011_100</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>INDEX</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>USDA National Agricultural Statistics Service (Quick Stats)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>US-PD</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>Source: USDA National Agricultural Statistics Service (NASS), Quick Stats</t>
         </is>
@@ -4328,7 +4383,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4394,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
@@ -4434,7 +4489,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-31</t>
         </is>
       </c>
     </row>
